--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136648711</v>
+        <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>96773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536663</v>
+        <v>536575</v>
       </c>
       <c r="R2" t="n">
-        <v>6460838</v>
+        <v>6460919</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,19 +748,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,77 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136648711</t>
+          <t>https://artportalen.se/Sighting/136649436</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136649134</v>
+        <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>58167</v>
+        <v>96773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536625</v>
+        <v>536561</v>
       </c>
       <c r="R3" t="n">
-        <v>6460940</v>
+        <v>6460962</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,19 +850,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,74 +867,62 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649134</t>
+          <t>https://artportalen.se/Sighting/136649571</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136652464</v>
+        <v>136649649</v>
       </c>
       <c r="B4" t="n">
-        <v>99342</v>
+        <v>81132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6444</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536584</v>
+        <v>536540</v>
       </c>
       <c r="R4" t="n">
-        <v>6460656</v>
+        <v>6460973</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,84 +963,83 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hugo Axelsson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Gabriel Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652464</t>
+          <t>https://artportalen.se/Sighting/136649649</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136652514</v>
+        <v>136648711</v>
       </c>
       <c r="B5" t="n">
-        <v>99342</v>
+        <v>58003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laggerbo, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536634</v>
+        <v>536663</v>
       </c>
       <c r="R5" t="n">
-        <v>6460956</v>
+        <v>6460838</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,92 +1066,97 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hugo Axelsson</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Gabriel Johansson, Emma Nordenberg</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652514</t>
+          <t>https://artportalen.se/Sighting/136648711</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136652550</v>
+        <v>136648818</v>
       </c>
       <c r="B6" t="n">
-        <v>99342</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Laggerbo, Ög</t>
+          <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536651</v>
+        <v>536633</v>
       </c>
       <c r="R6" t="n">
-        <v>6460952</v>
+        <v>6460901</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,84 +1197,79 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hugo Axelsson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652550</t>
+          <t>https://artportalen.se/Sighting/136648818</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136652570</v>
+        <v>136667373</v>
       </c>
       <c r="B7" t="n">
-        <v>99342</v>
+        <v>58003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Laggerbo, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536636</v>
+        <v>536575</v>
       </c>
       <c r="R7" t="n">
-        <v>6460926</v>
+        <v>6460674</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,81 +1307,68 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hugo Axelsson</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652570</t>
+          <t>https://artportalen.se/Sighting/136667373</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136652576</v>
+        <v>136647577</v>
       </c>
       <c r="B8" t="n">
-        <v>99342</v>
+        <v>58281</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103019</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Laggerbo, Ög</t>
+          <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536640</v>
+        <v>536527</v>
       </c>
       <c r="R8" t="n">
-        <v>6460944</v>
+        <v>6460658</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,84 +1409,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hugo Axelsson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652576</t>
+          <t>https://artportalen.se/Sighting/136647577</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136647428</v>
+        <v>136649083</v>
       </c>
       <c r="B9" t="n">
-        <v>106483</v>
+        <v>58167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536592</v>
+        <v>536631</v>
       </c>
       <c r="R9" t="n">
-        <v>6460674</v>
+        <v>6460927</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,19 +1500,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,77 +1517,77 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647428</t>
+          <t>https://artportalen.se/Sighting/136649083</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136647782</v>
+        <v>136649134</v>
       </c>
       <c r="B10" t="n">
-        <v>101552</v>
+        <v>58167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källtorpet, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536548</v>
+        <v>536625</v>
       </c>
       <c r="R10" t="n">
-        <v>6460724</v>
+        <v>6460940</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1744,6 +1651,2447 @@
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136649134</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136647128</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>536582</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6460672</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136647128</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136667188</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Laggarebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>536621</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6460604</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136667188</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136667213</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Laggarebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>536668</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6460606</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136667213</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136649596</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58870</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Laggarebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>536561</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6460962</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136649596</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136647103</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>536582</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6460672</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136647103</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136647324</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>536599</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6460650</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136647324</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136648296</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>536558</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6460695</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136648296</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136648316</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>536565</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6460703</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136648316</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136648763</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>536638</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6460861</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136648763</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136649129</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>536631</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6460927</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136649129</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136649150</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Laggarebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>536644</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6460954</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136649150</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136649188</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Laggarebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>536590</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6460954</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136649188</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136652464</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Laggarebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>536584</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6460656</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson, Gabriel Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136652464</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136652514</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Laggerbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>536634</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6460956</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson, Gabriel Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136652514</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136652550</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Laggerbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>536651</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6460952</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136652550</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136652570</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Laggerbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>536636</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6460926</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136652570</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136652576</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Laggerbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>536640</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6460944</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136652576</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136646823</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106483</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>536599</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6460624</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136646823</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136647428</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106483</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>536592</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6460674</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136647428</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136647297</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98204</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>536565</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6460664</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136647297</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136650172</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98204</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Laggarebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>536522</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6460989</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136650172</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136647782</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101552</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>536548</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6460724</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136647782</t>
         </is>
@@ -1760,6 +4108,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136647103</v>
       </c>
       <c r="B15" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>136647324</v>
       </c>
       <c r="B16" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136648296</v>
       </c>
       <c r="B17" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136648316</v>
       </c>
       <c r="B18" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136648763</v>
       </c>
       <c r="B19" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136649129</v>
       </c>
       <c r="B20" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>136649150</v>
       </c>
       <c r="B21" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>136649188</v>
       </c>
       <c r="B22" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>136652464</v>
       </c>
       <c r="B23" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>136652514</v>
       </c>
       <c r="B24" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>136652550</v>
       </c>
       <c r="B25" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>136652570</v>
       </c>
       <c r="B26" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>136652576</v>
       </c>
       <c r="B27" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>136646823</v>
       </c>
       <c r="B28" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136647428</v>
       </c>
       <c r="B29" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136647297</v>
       </c>
       <c r="B30" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>136650172</v>
       </c>
       <c r="B31" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>136647782</v>
       </c>
       <c r="B32" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136647103</v>
       </c>
       <c r="B15" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>136647324</v>
       </c>
       <c r="B16" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136648296</v>
       </c>
       <c r="B17" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136648316</v>
       </c>
       <c r="B18" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136648763</v>
       </c>
       <c r="B19" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136649129</v>
       </c>
       <c r="B20" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>136649150</v>
       </c>
       <c r="B21" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>136649188</v>
       </c>
       <c r="B22" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>136652464</v>
       </c>
       <c r="B23" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>136652514</v>
       </c>
       <c r="B24" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>136652550</v>
       </c>
       <c r="B25" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
         <v>136652570</v>
       </c>
       <c r="B26" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3433,7 +3433,7 @@
         <v>136652576</v>
       </c>
       <c r="B27" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>136646823</v>
       </c>
       <c r="B28" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136647428</v>
       </c>
       <c r="B29" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136647297</v>
       </c>
       <c r="B30" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>136650172</v>
       </c>
       <c r="B31" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>136647782</v>
       </c>
       <c r="B32" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136649649</v>
       </c>
       <c r="B4" t="n">
-        <v>81132</v>
+        <v>81134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136648711</v>
       </c>
       <c r="B5" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>136648818</v>
       </c>
       <c r="B6" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136667373</v>
       </c>
       <c r="B7" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>136647577</v>
       </c>
       <c r="B8" t="n">
-        <v>58281</v>
+        <v>58283</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>136649083</v>
       </c>
       <c r="B9" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>136649134</v>
       </c>
       <c r="B10" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>136649596</v>
       </c>
       <c r="B14" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136647103</v>
       </c>
       <c r="B15" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>136647324</v>
       </c>
       <c r="B16" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136648296</v>
       </c>
       <c r="B17" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136648316</v>
       </c>
       <c r="B18" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136648763</v>
       </c>
       <c r="B19" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136649129</v>
       </c>
       <c r="B20" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>136649150</v>
       </c>
       <c r="B21" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>136649188</v>
       </c>
       <c r="B22" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>136652464</v>
       </c>
       <c r="B23" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>136652514</v>
       </c>
       <c r="B24" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>136652550</v>
       </c>
       <c r="B25" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
         <v>136652570</v>
       </c>
       <c r="B26" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3433,7 +3433,7 @@
         <v>136652576</v>
       </c>
       <c r="B27" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>136646823</v>
       </c>
       <c r="B28" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136647428</v>
       </c>
       <c r="B29" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136647297</v>
       </c>
       <c r="B30" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>136650172</v>
       </c>
       <c r="B31" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>136647782</v>
       </c>
       <c r="B32" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96782</v>
+        <v>96784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96782</v>
+        <v>96784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
         <v>136647103</v>
       </c>
       <c r="B15" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>136647324</v>
       </c>
       <c r="B16" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136648296</v>
       </c>
       <c r="B17" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136648316</v>
       </c>
       <c r="B18" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136648763</v>
       </c>
       <c r="B19" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136649129</v>
       </c>
       <c r="B20" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2747,7 +2747,7 @@
         <v>136649150</v>
       </c>
       <c r="B21" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>136649188</v>
       </c>
       <c r="B22" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2973,7 +2973,7 @@
         <v>136652464</v>
       </c>
       <c r="B23" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>136652514</v>
       </c>
       <c r="B24" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>136652550</v>
       </c>
       <c r="B25" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>136652570</v>
       </c>
       <c r="B26" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>136652576</v>
       </c>
       <c r="B27" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>136646823</v>
       </c>
       <c r="B28" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136647428</v>
       </c>
       <c r="B29" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136647297</v>
       </c>
       <c r="B30" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>136650172</v>
       </c>
       <c r="B31" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>136647782</v>
       </c>
       <c r="B32" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136649649</v>
+        <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>81134</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6444</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skriftlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Graphis scripta</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Laggarebo, Ög</t>
+          <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536540</v>
+        <v>536688</v>
       </c>
       <c r="R4" t="n">
-        <v>6460973</v>
+        <v>6460661</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +979,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>krister wall</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>krister wall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649649</t>
+          <t>https://artportalen.se/Sighting/136985671</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136648711</v>
+        <v>136649649</v>
       </c>
       <c r="B5" t="n">
-        <v>58005</v>
+        <v>81134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,49 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6444</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536663</v>
+        <v>536540</v>
       </c>
       <c r="R5" t="n">
-        <v>6460838</v>
+        <v>6460973</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,19 +1064,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,24 +1081,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136648711</t>
+          <t>https://artportalen.se/Sighting/136649649</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136648818</v>
+        <v>136648711</v>
       </c>
       <c r="B6" t="n">
         <v>58005</v>
@@ -1138,28 +1126,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källtorpet, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536633</v>
+        <v>536663</v>
       </c>
       <c r="R6" t="n">
-        <v>6460901</v>
+        <v>6460838</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,9 +1178,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,24 +1205,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136648818</t>
+          <t>https://artportalen.se/Sighting/136648711</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136667373</v>
+        <v>136648818</v>
       </c>
       <c r="B7" t="n">
         <v>58005</v>
@@ -1253,23 +1255,23 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Laggarebo, Ög</t>
+          <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536575</v>
+        <v>536633</v>
       </c>
       <c r="R7" t="n">
-        <v>6460674</v>
+        <v>6460901</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,27 +1315,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136667373</t>
+          <t>https://artportalen.se/Sighting/136648818</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136647577</v>
+        <v>136667373</v>
       </c>
       <c r="B8" t="n">
-        <v>58283</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,16 +1343,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103019</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärtmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Aegithalos caudatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1359,19 +1361,27 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källtorpet, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536527</v>
+        <v>536575</v>
       </c>
       <c r="R8" t="n">
-        <v>6460658</v>
+        <v>6460674</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,49 +1425,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647577</t>
+          <t>https://artportalen.se/Sighting/136667373</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136649083</v>
+        <v>136647577</v>
       </c>
       <c r="B9" t="n">
-        <v>58169</v>
+        <v>58283</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103019</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536631</v>
+        <v>536527</v>
       </c>
       <c r="R9" t="n">
-        <v>6460927</v>
+        <v>6460658</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,13 +1538,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649083</t>
+          <t>https://artportalen.se/Sighting/136647577</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136649134</v>
+        <v>136649083</v>
       </c>
       <c r="B10" t="n">
         <v>58169</v>
@@ -1562,32 +1572,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Laggarebo, Ög</t>
+          <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536625</v>
+        <v>536631</v>
       </c>
       <c r="R10" t="n">
-        <v>6460940</v>
+        <v>6460927</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1614,19 +1612,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,65 +1629,77 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649134</t>
+          <t>https://artportalen.se/Sighting/136649083</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136647128</v>
+        <v>136649134</v>
       </c>
       <c r="B11" t="n">
-        <v>8463</v>
+        <v>58169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källtorpet, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536582</v>
+        <v>536625</v>
       </c>
       <c r="R11" t="n">
-        <v>6460672</v>
+        <v>6460940</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,9 +1726,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,24 +1753,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647128</t>
+          <t>https://artportalen.se/Sighting/136649134</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136667188</v>
+        <v>136647128</v>
       </c>
       <c r="B12" t="n">
         <v>8463</v>
@@ -1789,24 +1799,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Laggarebo, Ög</t>
+          <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536621</v>
+        <v>536582</v>
       </c>
       <c r="R12" t="n">
-        <v>6460604</v>
+        <v>6460672</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,31 +1849,30 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136667188</t>
+          <t>https://artportalen.se/Sighting/136647128</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136667213</v>
+        <v>136667188</v>
       </c>
       <c r="B13" t="n">
         <v>8463</v>
@@ -1908,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536668</v>
+        <v>536621</v>
       </c>
       <c r="R13" t="n">
-        <v>6460606</v>
+        <v>6460604</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1970,16 +1974,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136667213</t>
+          <t>https://artportalen.se/Sighting/136667188</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136649596</v>
+        <v>136667213</v>
       </c>
       <c r="B14" t="n">
-        <v>58872</v>
+        <v>8463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1987,37 +1991,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536561</v>
+        <v>536668</v>
       </c>
       <c r="R14" t="n">
-        <v>6460962</v>
+        <v>6460606</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2055,77 +2064,69 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649596</t>
+          <t>https://artportalen.se/Sighting/136667213</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136647103</v>
+        <v>136649596</v>
       </c>
       <c r="B15" t="n">
-        <v>99353</v>
+        <v>58872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källtorpet, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536582</v>
+        <v>536561</v>
       </c>
       <c r="R15" t="n">
-        <v>6460672</v>
+        <v>6460962</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,13 +2184,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647103</t>
+          <t>https://artportalen.se/Sighting/136649596</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136647324</v>
+        <v>136647103</v>
       </c>
       <c r="B16" t="n">
         <v>99353</v>
@@ -2219,7 +2220,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2233,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536599</v>
+        <v>536582</v>
       </c>
       <c r="R16" t="n">
-        <v>6460650</v>
+        <v>6460672</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,13 +2295,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647324</t>
+          <t>https://artportalen.se/Sighting/136647103</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136648296</v>
+        <v>136647324</v>
       </c>
       <c r="B17" t="n">
         <v>99353</v>
@@ -2330,7 +2331,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2344,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536558</v>
+        <v>536599</v>
       </c>
       <c r="R17" t="n">
-        <v>6460695</v>
+        <v>6460650</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,13 +2406,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136648296</t>
+          <t>https://artportalen.se/Sighting/136647324</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136648316</v>
+        <v>136648296</v>
       </c>
       <c r="B18" t="n">
         <v>99353</v>
@@ -2441,7 +2442,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2455,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536565</v>
+        <v>536558</v>
       </c>
       <c r="R18" t="n">
-        <v>6460703</v>
+        <v>6460695</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,13 +2517,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136648316</t>
+          <t>https://artportalen.se/Sighting/136648296</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136648763</v>
+        <v>136648316</v>
       </c>
       <c r="B19" t="n">
         <v>99353</v>
@@ -2552,7 +2553,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2566,10 +2567,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536638</v>
+        <v>536565</v>
       </c>
       <c r="R19" t="n">
-        <v>6460861</v>
+        <v>6460703</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,13 +2628,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136648763</t>
+          <t>https://artportalen.se/Sighting/136648316</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136649129</v>
+        <v>136648763</v>
       </c>
       <c r="B20" t="n">
         <v>99353</v>
@@ -2663,7 +2664,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2677,10 +2678,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536631</v>
+        <v>536638</v>
       </c>
       <c r="R20" t="n">
-        <v>6460927</v>
+        <v>6460861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,13 +2739,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649129</t>
+          <t>https://artportalen.se/Sighting/136648763</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136649150</v>
+        <v>136649129</v>
       </c>
       <c r="B21" t="n">
         <v>99353</v>
@@ -2774,7 +2775,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2782,19 +2783,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Laggarebo, Ög</t>
+          <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536644</v>
+        <v>536631</v>
       </c>
       <c r="R21" t="n">
-        <v>6460954</v>
+        <v>6460927</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2835,7 +2833,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2847,19 +2844,19 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649150</t>
+          <t>https://artportalen.se/Sighting/136649129</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136649188</v>
+        <v>136649150</v>
       </c>
       <c r="B22" t="n">
         <v>99353</v>
@@ -2889,7 +2886,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2897,19 +2894,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536590</v>
+        <v>536644</v>
       </c>
       <c r="R22" t="n">
         <v>6460954</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2947,6 +2947,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2958,19 +2959,19 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649188</t>
+          <t>https://artportalen.se/Sighting/136649150</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136652464</v>
+        <v>136649188</v>
       </c>
       <c r="B23" t="n">
         <v>99353</v>
@@ -3000,30 +3001,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536584</v>
+        <v>536590</v>
       </c>
       <c r="R23" t="n">
-        <v>6460656</v>
+        <v>6460954</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3061,31 +3059,30 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hugo Axelsson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Gabriel Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652464</t>
+          <t>https://artportalen.se/Sighting/136649188</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136652514</v>
+        <v>136652464</v>
       </c>
       <c r="B24" t="n">
         <v>99353</v>
@@ -3115,7 +3112,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3128,14 +3125,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Laggerbo, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536634</v>
+        <v>536584</v>
       </c>
       <c r="R24" t="n">
-        <v>6460956</v>
+        <v>6460656</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3194,13 +3191,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652514</t>
+          <t>https://artportalen.se/Sighting/136652464</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136652550</v>
+        <v>136652514</v>
       </c>
       <c r="B25" t="n">
         <v>99353</v>
@@ -3230,7 +3227,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3247,10 +3244,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536651</v>
+        <v>536634</v>
       </c>
       <c r="R25" t="n">
-        <v>6460952</v>
+        <v>6460956</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3303,19 +3300,19 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Hugo Axelsson, Gabriel Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652550</t>
+          <t>https://artportalen.se/Sighting/136652514</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136652570</v>
+        <v>136652550</v>
       </c>
       <c r="B26" t="n">
         <v>99353</v>
@@ -3345,7 +3342,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3362,10 +3359,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536636</v>
+        <v>536651</v>
       </c>
       <c r="R26" t="n">
-        <v>6460926</v>
+        <v>6460952</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3424,13 +3421,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652570</t>
+          <t>https://artportalen.se/Sighting/136652550</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136652576</v>
+        <v>136652570</v>
       </c>
       <c r="B27" t="n">
         <v>99353</v>
@@ -3460,7 +3457,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3477,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536640</v>
+        <v>536636</v>
       </c>
       <c r="R27" t="n">
-        <v>6460944</v>
+        <v>6460926</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3539,51 +3536,63 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652576</t>
+          <t>https://artportalen.se/Sighting/136652570</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136646823</v>
+        <v>136652576</v>
       </c>
       <c r="B28" t="n">
-        <v>106494</v>
+        <v>99353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Källtorpet, Ög</t>
+          <t>Laggerbo, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536599</v>
+        <v>536640</v>
       </c>
       <c r="R28" t="n">
-        <v>6460624</v>
+        <v>6460944</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3624,30 +3633,31 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Hugo Axelsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136646823</t>
+          <t>https://artportalen.se/Sighting/136652576</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136647428</v>
+        <v>136646823</v>
       </c>
       <c r="B29" t="n">
         <v>106494</v>
@@ -3675,32 +3685,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536592</v>
+        <v>536599</v>
       </c>
       <c r="R29" t="n">
-        <v>6460674</v>
+        <v>6460624</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3727,19 +3725,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3754,27 +3742,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647428</t>
+          <t>https://artportalen.se/Sighting/136646823</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136647297</v>
+        <v>136647428</v>
       </c>
       <c r="B30" t="n">
-        <v>98215</v>
+        <v>106494</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,37 +3770,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536565</v>
+        <v>536592</v>
       </c>
       <c r="R30" t="n">
-        <v>6460664</v>
+        <v>6460674</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3839,9 +3839,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,24 +3866,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647297</t>
+          <t>https://artportalen.se/Sighting/136647428</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136650172</v>
+        <v>136647297</v>
       </c>
       <c r="B31" t="n">
         <v>98215</v>
@@ -3904,14 +3914,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Laggarebo, Ög</t>
+          <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536522</v>
+        <v>536565</v>
       </c>
       <c r="R31" t="n">
-        <v>6460989</v>
+        <v>6460664</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3969,16 +3979,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136650172</t>
+          <t>https://artportalen.se/Sighting/136647297</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136647782</v>
+        <v>136650172</v>
       </c>
       <c r="B32" t="n">
-        <v>101563</v>
+        <v>98215</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,49 +3996,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källtorpet, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536548</v>
+        <v>536522</v>
       </c>
       <c r="R32" t="n">
-        <v>6460724</v>
+        <v>6460989</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4055,19 +4053,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4082,16 +4070,140 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136650172</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136647782</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>536548</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6460724</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136647782</t>
         </is>
@@ -4130,6 +4242,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136649649</v>
       </c>
       <c r="B5" t="n">
-        <v>81134</v>
+        <v>81138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>136647103</v>
       </c>
       <c r="B16" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>136647324</v>
       </c>
       <c r="B17" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136648296</v>
       </c>
       <c r="B18" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>136648316</v>
       </c>
       <c r="B19" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>136648763</v>
       </c>
       <c r="B20" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136649129</v>
       </c>
       <c r="B21" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>136649150</v>
       </c>
       <c r="B22" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136649188</v>
       </c>
       <c r="B23" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136652464</v>
       </c>
       <c r="B24" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136652514</v>
       </c>
       <c r="B25" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136652550</v>
       </c>
       <c r="B26" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3430,7 +3430,7 @@
         <v>136652570</v>
       </c>
       <c r="B27" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>136652576</v>
       </c>
       <c r="B28" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>136646823</v>
       </c>
       <c r="B29" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>136647428</v>
       </c>
       <c r="B30" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>136647297</v>
       </c>
       <c r="B31" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>136650172</v>
       </c>
       <c r="B32" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4090,7 +4090,7 @@
         <v>136647782</v>
       </c>
       <c r="B33" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92340</v>
+        <v>92342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136649649</v>
       </c>
       <c r="B5" t="n">
-        <v>81138</v>
+        <v>81140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>136647103</v>
       </c>
       <c r="B16" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>136647324</v>
       </c>
       <c r="B17" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136648296</v>
       </c>
       <c r="B18" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>136648316</v>
       </c>
       <c r="B19" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>136648763</v>
       </c>
       <c r="B20" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136649129</v>
       </c>
       <c r="B21" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>136649150</v>
       </c>
       <c r="B22" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136649188</v>
       </c>
       <c r="B23" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136652464</v>
       </c>
       <c r="B24" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136652514</v>
       </c>
       <c r="B25" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136652550</v>
       </c>
       <c r="B26" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3430,7 +3430,7 @@
         <v>136652570</v>
       </c>
       <c r="B27" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>136652576</v>
       </c>
       <c r="B28" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>136646823</v>
       </c>
       <c r="B29" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>136647428</v>
       </c>
       <c r="B30" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>136647297</v>
       </c>
       <c r="B31" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>136650172</v>
       </c>
       <c r="B32" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4090,7 +4090,7 @@
         <v>136647782</v>
       </c>
       <c r="B33" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1770,45 +1770,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136647128</v>
+        <v>137090514</v>
       </c>
       <c r="B12" t="n">
-        <v>8463</v>
+        <v>58169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källtorpet, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536582</v>
+        <v>536597</v>
       </c>
       <c r="R12" t="n">
-        <v>6460672</v>
+        <v>6460855</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,24 +1863,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647128</t>
+          <t>https://artportalen.se/Sighting/137090514</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136667188</v>
+        <v>136647128</v>
       </c>
       <c r="B13" t="n">
         <v>8463</v>
@@ -1901,24 +1909,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Laggarebo, Ög</t>
+          <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536621</v>
+        <v>536582</v>
       </c>
       <c r="R13" t="n">
-        <v>6460604</v>
+        <v>6460672</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1956,31 +1959,30 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136667188</t>
+          <t>https://artportalen.se/Sighting/136647128</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136667213</v>
+        <v>136667188</v>
       </c>
       <c r="B14" t="n">
         <v>8463</v>
@@ -2020,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536668</v>
+        <v>536621</v>
       </c>
       <c r="R14" t="n">
-        <v>6460606</v>
+        <v>6460604</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2082,16 +2084,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136667213</t>
+          <t>https://artportalen.se/Sighting/136667188</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136649596</v>
+        <v>136667213</v>
       </c>
       <c r="B15" t="n">
-        <v>58872</v>
+        <v>8463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,37 +2101,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208249</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536561</v>
+        <v>536668</v>
       </c>
       <c r="R15" t="n">
-        <v>6460962</v>
+        <v>6460606</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2167,77 +2174,69 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Hugo Axelsson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649596</t>
+          <t>https://artportalen.se/Sighting/136667213</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136647103</v>
+        <v>136649596</v>
       </c>
       <c r="B16" t="n">
-        <v>99361</v>
+        <v>58872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källtorpet, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536582</v>
+        <v>536561</v>
       </c>
       <c r="R16" t="n">
-        <v>6460672</v>
+        <v>6460962</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,13 +2294,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647103</t>
+          <t>https://artportalen.se/Sighting/136649596</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136647324</v>
+        <v>136647103</v>
       </c>
       <c r="B17" t="n">
         <v>99361</v>
@@ -2331,7 +2330,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2345,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536599</v>
+        <v>536582</v>
       </c>
       <c r="R17" t="n">
-        <v>6460650</v>
+        <v>6460672</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,13 +2405,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647324</t>
+          <t>https://artportalen.se/Sighting/136647103</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136648296</v>
+        <v>136647324</v>
       </c>
       <c r="B18" t="n">
         <v>99361</v>
@@ -2442,7 +2441,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2456,10 +2455,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536558</v>
+        <v>536599</v>
       </c>
       <c r="R18" t="n">
-        <v>6460695</v>
+        <v>6460650</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,13 +2516,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136648296</t>
+          <t>https://artportalen.se/Sighting/136647324</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136648316</v>
+        <v>136648296</v>
       </c>
       <c r="B19" t="n">
         <v>99361</v>
@@ -2553,7 +2552,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2567,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536565</v>
+        <v>536558</v>
       </c>
       <c r="R19" t="n">
-        <v>6460703</v>
+        <v>6460695</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,13 +2627,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136648316</t>
+          <t>https://artportalen.se/Sighting/136648296</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136648763</v>
+        <v>136648316</v>
       </c>
       <c r="B20" t="n">
         <v>99361</v>
@@ -2664,7 +2663,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2678,10 +2677,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536638</v>
+        <v>536565</v>
       </c>
       <c r="R20" t="n">
-        <v>6460861</v>
+        <v>6460703</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,13 +2738,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136648763</t>
+          <t>https://artportalen.se/Sighting/136648316</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136649129</v>
+        <v>136648763</v>
       </c>
       <c r="B21" t="n">
         <v>99361</v>
@@ -2775,7 +2774,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2789,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536631</v>
+        <v>536638</v>
       </c>
       <c r="R21" t="n">
-        <v>6460927</v>
+        <v>6460861</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,13 +2849,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649129</t>
+          <t>https://artportalen.se/Sighting/136648763</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136649150</v>
+        <v>136649129</v>
       </c>
       <c r="B22" t="n">
         <v>99361</v>
@@ -2886,7 +2885,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2894,19 +2893,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Laggarebo, Ög</t>
+          <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536644</v>
+        <v>536631</v>
       </c>
       <c r="R22" t="n">
-        <v>6460954</v>
+        <v>6460927</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2947,7 +2943,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2959,19 +2954,19 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649150</t>
+          <t>https://artportalen.se/Sighting/136649129</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136649188</v>
+        <v>136649150</v>
       </c>
       <c r="B23" t="n">
         <v>99361</v>
@@ -3001,7 +2996,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3009,19 +3004,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536590</v>
+        <v>536644</v>
       </c>
       <c r="R23" t="n">
         <v>6460954</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3059,6 +3057,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3070,19 +3069,19 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136649188</t>
+          <t>https://artportalen.se/Sighting/136649150</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136652464</v>
+        <v>136649188</v>
       </c>
       <c r="B24" t="n">
         <v>99361</v>
@@ -3112,30 +3111,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536584</v>
+        <v>536590</v>
       </c>
       <c r="R24" t="n">
-        <v>6460656</v>
+        <v>6460954</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,31 +3169,30 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hugo Axelsson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Gabriel Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652464</t>
+          <t>https://artportalen.se/Sighting/136649188</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136652514</v>
+        <v>136652464</v>
       </c>
       <c r="B25" t="n">
         <v>99361</v>
@@ -3227,7 +3222,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3240,14 +3235,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Laggerbo, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536634</v>
+        <v>536584</v>
       </c>
       <c r="R25" t="n">
-        <v>6460956</v>
+        <v>6460656</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3306,13 +3301,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652514</t>
+          <t>https://artportalen.se/Sighting/136652464</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136652550</v>
+        <v>136652514</v>
       </c>
       <c r="B26" t="n">
         <v>99361</v>
@@ -3342,7 +3337,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3359,10 +3354,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536651</v>
+        <v>536634</v>
       </c>
       <c r="R26" t="n">
-        <v>6460952</v>
+        <v>6460956</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,19 +3410,19 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Hugo Axelsson, Gabriel Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652550</t>
+          <t>https://artportalen.se/Sighting/136652514</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136652570</v>
+        <v>136652550</v>
       </c>
       <c r="B27" t="n">
         <v>99361</v>
@@ -3457,7 +3452,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3474,10 +3469,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536636</v>
+        <v>536651</v>
       </c>
       <c r="R27" t="n">
-        <v>6460926</v>
+        <v>6460952</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3536,13 +3531,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652570</t>
+          <t>https://artportalen.se/Sighting/136652550</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136652576</v>
+        <v>136652570</v>
       </c>
       <c r="B28" t="n">
         <v>99361</v>
@@ -3572,7 +3567,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536640</v>
+        <v>536636</v>
       </c>
       <c r="R28" t="n">
-        <v>6460944</v>
+        <v>6460926</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3651,51 +3646,63 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136652576</t>
+          <t>https://artportalen.se/Sighting/136652570</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136646823</v>
+        <v>136652576</v>
       </c>
       <c r="B29" t="n">
-        <v>106502</v>
+        <v>99361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Källtorpet, Ög</t>
+          <t>Laggerbo, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536599</v>
+        <v>536640</v>
       </c>
       <c r="R29" t="n">
-        <v>6460624</v>
+        <v>6460944</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3736,30 +3743,31 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Hugo Axelsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136646823</t>
+          <t>https://artportalen.se/Sighting/136652576</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136647428</v>
+        <v>136646823</v>
       </c>
       <c r="B30" t="n">
         <v>106502</v>
@@ -3787,32 +3795,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536592</v>
+        <v>536599</v>
       </c>
       <c r="R30" t="n">
-        <v>6460674</v>
+        <v>6460624</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3839,19 +3835,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3866,27 +3852,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647428</t>
+          <t>https://artportalen.se/Sighting/136646823</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136647297</v>
+        <v>136647428</v>
       </c>
       <c r="B31" t="n">
-        <v>98223</v>
+        <v>106502</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,37 +3880,49 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536565</v>
+        <v>536592</v>
       </c>
       <c r="R31" t="n">
-        <v>6460664</v>
+        <v>6460674</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3951,9 +3949,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,24 +3976,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136647297</t>
+          <t>https://artportalen.se/Sighting/136647428</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136650172</v>
+        <v>136647297</v>
       </c>
       <c r="B32" t="n">
         <v>98223</v>
@@ -4016,14 +4024,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Laggarebo, Ög</t>
+          <t>Källtorpet, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536522</v>
+        <v>536565</v>
       </c>
       <c r="R32" t="n">
-        <v>6460989</v>
+        <v>6460664</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4081,16 +4089,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136650172</t>
+          <t>https://artportalen.se/Sighting/136647297</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136647782</v>
+        <v>136650172</v>
       </c>
       <c r="B33" t="n">
-        <v>101571</v>
+        <v>98223</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4098,49 +4106,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källtorpet, Ög</t>
+          <t>Laggarebo, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536548</v>
+        <v>536522</v>
       </c>
       <c r="R33" t="n">
-        <v>6460724</v>
+        <v>6460989</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4167,19 +4163,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4194,16 +4180,140 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136650172</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136647782</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Källtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>536548</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6460724</v>
+      </c>
+      <c r="S34" t="n">
+        <v>8</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136647782</t>
         </is>
@@ -4243,6 +4353,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92342</v>
+        <v>92343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136649649</v>
       </c>
       <c r="B5" t="n">
-        <v>81140</v>
+        <v>81141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136647103</v>
       </c>
       <c r="B17" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136647324</v>
       </c>
       <c r="B18" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136648296</v>
       </c>
       <c r="B19" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136648316</v>
       </c>
       <c r="B20" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>136648763</v>
       </c>
       <c r="B21" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136649129</v>
       </c>
       <c r="B22" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136649150</v>
       </c>
       <c r="B23" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136649188</v>
       </c>
       <c r="B24" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>136652464</v>
       </c>
       <c r="B25" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>136652514</v>
       </c>
       <c r="B26" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136652550</v>
       </c>
       <c r="B27" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3540,7 +3540,7 @@
         <v>136652570</v>
       </c>
       <c r="B28" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136652576</v>
       </c>
       <c r="B29" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136646823</v>
       </c>
       <c r="B30" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hugo Axelsson</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3872,7 +3872,7 @@
         <v>136647428</v>
       </c>
       <c r="B31" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>136647297</v>
       </c>
       <c r="B32" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136650172</v>
       </c>
       <c r="B33" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>136647782</v>
       </c>
       <c r="B34" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92343</v>
+        <v>92349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136647103</v>
       </c>
       <c r="B17" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136647324</v>
       </c>
       <c r="B18" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136648296</v>
       </c>
       <c r="B19" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136648316</v>
       </c>
       <c r="B20" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>136648763</v>
       </c>
       <c r="B21" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136649129</v>
       </c>
       <c r="B22" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136649150</v>
       </c>
       <c r="B23" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136649188</v>
       </c>
       <c r="B24" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>136652464</v>
       </c>
       <c r="B25" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>136652514</v>
       </c>
       <c r="B26" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136652550</v>
       </c>
       <c r="B27" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>136652570</v>
       </c>
       <c r="B28" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136652576</v>
       </c>
       <c r="B29" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136646823</v>
       </c>
       <c r="B30" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>136647428</v>
       </c>
       <c r="B31" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>136647297</v>
       </c>
       <c r="B32" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136650172</v>
       </c>
       <c r="B33" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>136647782</v>
       </c>
       <c r="B34" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92349</v>
+        <v>92353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136649649</v>
       </c>
       <c r="B5" t="n">
-        <v>81141</v>
+        <v>81143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136647103</v>
       </c>
       <c r="B17" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136647324</v>
       </c>
       <c r="B18" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136648296</v>
       </c>
       <c r="B19" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136648316</v>
       </c>
       <c r="B20" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>136648763</v>
       </c>
       <c r="B21" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136649129</v>
       </c>
       <c r="B22" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136649150</v>
       </c>
       <c r="B23" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136649188</v>
       </c>
       <c r="B24" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>136652464</v>
       </c>
       <c r="B25" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>136652514</v>
       </c>
       <c r="B26" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136652550</v>
       </c>
       <c r="B27" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>136652570</v>
       </c>
       <c r="B28" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136652576</v>
       </c>
       <c r="B29" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136646823</v>
       </c>
       <c r="B30" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>136647428</v>
       </c>
       <c r="B31" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>136647297</v>
       </c>
       <c r="B32" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136650172</v>
       </c>
       <c r="B33" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>136647782</v>
       </c>
       <c r="B34" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136647103</v>
       </c>
       <c r="B17" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136647324</v>
       </c>
       <c r="B18" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136648296</v>
       </c>
       <c r="B19" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136648316</v>
       </c>
       <c r="B20" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>136648763</v>
       </c>
       <c r="B21" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136649129</v>
       </c>
       <c r="B22" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136649150</v>
       </c>
       <c r="B23" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136649188</v>
       </c>
       <c r="B24" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>136652464</v>
       </c>
       <c r="B25" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>136652514</v>
       </c>
       <c r="B26" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136652550</v>
       </c>
       <c r="B27" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3540,7 +3540,7 @@
         <v>136652570</v>
       </c>
       <c r="B28" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3655,7 +3655,7 @@
         <v>136652576</v>
       </c>
       <c r="B29" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136646823</v>
       </c>
       <c r="B30" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>136647428</v>
       </c>
       <c r="B31" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>136647297</v>
       </c>
       <c r="B32" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136650172</v>
       </c>
       <c r="B33" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>136647782</v>
       </c>
       <c r="B34" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92353</v>
+        <v>92355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136649649</v>
       </c>
       <c r="B5" t="n">
-        <v>81143</v>
+        <v>81146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136647103</v>
       </c>
       <c r="B17" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136647324</v>
       </c>
       <c r="B18" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136648296</v>
       </c>
       <c r="B19" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136648316</v>
       </c>
       <c r="B20" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>136648763</v>
       </c>
       <c r="B21" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136649129</v>
       </c>
       <c r="B22" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136649150</v>
       </c>
       <c r="B23" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136649188</v>
       </c>
       <c r="B24" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>136652464</v>
       </c>
       <c r="B25" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>136652514</v>
       </c>
       <c r="B26" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136652550</v>
       </c>
       <c r="B27" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3540,7 +3540,7 @@
         <v>136652570</v>
       </c>
       <c r="B28" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3655,7 +3655,7 @@
         <v>136652576</v>
       </c>
       <c r="B29" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3770,7 +3770,7 @@
         <v>136646823</v>
       </c>
       <c r="B30" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>136647428</v>
       </c>
       <c r="B31" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>136647297</v>
       </c>
       <c r="B32" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136650172</v>
       </c>
       <c r="B33" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>136647782</v>
       </c>
       <c r="B34" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92355</v>
+        <v>92368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136649649</v>
       </c>
       <c r="B5" t="n">
-        <v>81146</v>
+        <v>81159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136648711</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136648818</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136667373</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136647577</v>
       </c>
       <c r="B9" t="n">
-        <v>58283</v>
+        <v>58296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136649083</v>
       </c>
       <c r="B10" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136649134</v>
       </c>
       <c r="B11" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137090514</v>
       </c>
       <c r="B12" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>136649596</v>
       </c>
       <c r="B16" t="n">
-        <v>58872</v>
+        <v>58885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136647103</v>
       </c>
       <c r="B17" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136647324</v>
       </c>
       <c r="B18" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136648296</v>
       </c>
       <c r="B19" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136648316</v>
       </c>
       <c r="B20" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>136648763</v>
       </c>
       <c r="B21" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136649129</v>
       </c>
       <c r="B22" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136649150</v>
       </c>
       <c r="B23" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136649188</v>
       </c>
       <c r="B24" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>136652464</v>
       </c>
       <c r="B25" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>136652514</v>
       </c>
       <c r="B26" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136652550</v>
       </c>
       <c r="B27" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>136652570</v>
       </c>
       <c r="B28" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3655,7 +3655,7 @@
         <v>136652576</v>
       </c>
       <c r="B29" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3770,7 +3770,7 @@
         <v>136646823</v>
       </c>
       <c r="B30" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>136647428</v>
       </c>
       <c r="B31" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>136647297</v>
       </c>
       <c r="B32" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136650172</v>
       </c>
       <c r="B33" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>136647782</v>
       </c>
       <c r="B34" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92368</v>
+        <v>92370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136649649</v>
       </c>
       <c r="B5" t="n">
-        <v>81159</v>
+        <v>81161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136648711</v>
       </c>
       <c r="B6" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136648818</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136667373</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136647577</v>
       </c>
       <c r="B9" t="n">
-        <v>58296</v>
+        <v>58298</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136649083</v>
       </c>
       <c r="B10" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136649134</v>
       </c>
       <c r="B11" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137090514</v>
       </c>
       <c r="B12" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136647128</v>
       </c>
       <c r="B13" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>136667188</v>
       </c>
       <c r="B14" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>136667213</v>
       </c>
       <c r="B15" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>136649596</v>
       </c>
       <c r="B16" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136647103</v>
       </c>
       <c r="B17" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136647324</v>
       </c>
       <c r="B18" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136648296</v>
       </c>
       <c r="B19" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136648316</v>
       </c>
       <c r="B20" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>136648763</v>
       </c>
       <c r="B21" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136649129</v>
       </c>
       <c r="B22" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136649150</v>
       </c>
       <c r="B23" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136649188</v>
       </c>
       <c r="B24" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>136652464</v>
       </c>
       <c r="B25" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>136652514</v>
       </c>
       <c r="B26" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136652550</v>
       </c>
       <c r="B27" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Emma Nordenberg, Hugo Axelsson</t>
+          <t>Hugo Axelsson, Emma Nordenberg, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3540,7 +3540,7 @@
         <v>136652570</v>
       </c>
       <c r="B28" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136652576</v>
       </c>
       <c r="B29" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136646823</v>
       </c>
       <c r="B30" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>136647428</v>
       </c>
       <c r="B31" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>136647297</v>
       </c>
       <c r="B32" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136650172</v>
       </c>
       <c r="B33" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>136647782</v>
       </c>
       <c r="B34" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -1253,11 +1253,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1363,11 +1359,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1801,11 +1793,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136649436</v>
       </c>
       <c r="B2" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136649571</v>
       </c>
       <c r="B3" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>136647103</v>
       </c>
       <c r="B17" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>136647324</v>
       </c>
       <c r="B18" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>136648296</v>
       </c>
       <c r="B19" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136648316</v>
       </c>
       <c r="B20" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>136648763</v>
       </c>
       <c r="B21" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>136649129</v>
       </c>
       <c r="B22" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>136649150</v>
       </c>
       <c r="B23" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136649188</v>
       </c>
       <c r="B24" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>136646823</v>
       </c>
       <c r="B30" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>136647297</v>
       </c>
       <c r="B32" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>136650172</v>
       </c>
       <c r="B33" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92373</v>
+        <v>92383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>137090514</v>
       </c>
       <c r="B12" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>137090514</v>
       </c>
       <c r="B12" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>137090514</v>
       </c>
       <c r="B12" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92410</v>
+        <v>92411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37483-2026 artfynd.xlsx
+++ b/artfynd/A 37483-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136985671</v>
       </c>
       <c r="B4" t="n">
-        <v>92411</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>137090514</v>
       </c>
       <c r="B12" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
